--- a/data/trans_dic/P8_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P8_1_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 12,36</t>
+          <t>6,8; 12,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 15,01</t>
+          <t>8,28; 14,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,34</t>
+          <t>7,51; 13,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,79</t>
+          <t>5,48; 9,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 18,97</t>
+          <t>11,19; 19,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 16,02</t>
+          <t>8,33; 16,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 16,1</t>
+          <t>8,38; 15,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,71</t>
+          <t>9,53; 14,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,75</t>
+          <t>9,29; 13,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 14,12</t>
+          <t>9,07; 14,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 13,23</t>
+          <t>8,68; 13,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,13</t>
+          <t>7,96; 11,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,7</t>
+          <t>3,13; 8,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,76</t>
+          <t>9,19; 16,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 13,55</t>
+          <t>7,02; 13,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 14,97</t>
+          <t>9,15; 15,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,69</t>
+          <t>3,7; 8,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,84</t>
+          <t>7,44; 14,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,41</t>
+          <t>7,2; 14,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,63; 17,16</t>
+          <t>11,71; 17,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,5</t>
+          <t>4,14; 7,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,17</t>
+          <t>9,16; 14,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,65</t>
+          <t>7,92; 12,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 15,08</t>
+          <t>10,98; 15,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 14,51</t>
+          <t>9,05; 14,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 20,3</t>
+          <t>13,89; 20,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,8</t>
+          <t>11,56; 17,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,4; 81,74</t>
+          <t>15,78; 79,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,92; 31,31</t>
+          <t>18,08; 30,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 30,95</t>
+          <t>19,94; 31,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,58; 31,63</t>
+          <t>17,15; 32,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 33,24</t>
+          <t>22,45; 33,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 17,22</t>
+          <t>12,13; 17,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 22,15</t>
+          <t>16,7; 22,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 20,02</t>
+          <t>14,08; 20,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 76,33</t>
+          <t>19,06; 73,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 16,54</t>
+          <t>12,85; 16,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,84; 19,52</t>
+          <t>14,84; 19,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 18,0</t>
+          <t>13,71; 18,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 21,0</t>
+          <t>16,04; 20,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 21,5</t>
+          <t>15,82; 21,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 18,88</t>
+          <t>13,18; 18,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 19,41</t>
+          <t>14,08; 19,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,62</t>
+          <t>7,12; 16,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 17,72</t>
+          <t>14,45; 17,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 18,32</t>
+          <t>14,87; 18,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 17,71</t>
+          <t>14,41; 17,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 18,13</t>
+          <t>10,66; 17,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 18,2</t>
+          <t>10,72; 17,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 20,68</t>
+          <t>14,34; 21,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,52</t>
+          <t>17,26; 23,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,85</t>
+          <t>17,53; 25,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,72; 23,28</t>
+          <t>16,67; 23,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,91; 37,15</t>
+          <t>30,25; 37,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,66; 32,21</t>
+          <t>25,19; 32,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,2; 30,08</t>
+          <t>19,5; 30,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,36</t>
+          <t>15,31; 20,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,49</t>
+          <t>24,69; 29,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,49; 27,22</t>
+          <t>22,68; 27,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,99; 27,13</t>
+          <t>19,72; 27,03</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,88</t>
+          <t>1,22; 4,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,83</t>
+          <t>1,84; 7,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,48</t>
+          <t>0,77; 4,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,41</t>
+          <t>0,65; 3,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,19; 32,51</t>
+          <t>27,03; 32,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,58; 37,42</t>
+          <t>31,44; 37,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,29; 33,4</t>
+          <t>27,16; 33,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,8; 34,41</t>
+          <t>28,96; 34,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,02; 26,43</t>
+          <t>22,38; 26,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,12; 31,08</t>
+          <t>25,95; 31,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,92; 26,89</t>
+          <t>22,0; 26,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,94; 26,8</t>
+          <t>22,03; 27,03</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,35</t>
+          <t>10,11; 12,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,23; 15,91</t>
+          <t>13,39; 16,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,69; 15,12</t>
+          <t>12,67; 15,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,24; 38,68</t>
+          <t>14,18; 35,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,08; 22,92</t>
+          <t>19,97; 22,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,78; 26,81</t>
+          <t>23,83; 26,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 24,07</t>
+          <t>21,16; 24,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,78; 22,58</t>
+          <t>16,82; 22,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,5; 17,26</t>
+          <t>15,58; 17,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 21,1</t>
+          <t>19,17; 21,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,35; 19,29</t>
+          <t>17,36; 19,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,41; 33,39</t>
+          <t>17,45; 30,76</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32095; 58550</t>
+          <t>32204; 58568</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35336; 65633</t>
+          <t>36200; 64185</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32433; 57251</t>
+          <t>32238; 56294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27474; 49439</t>
+          <t>27709; 50162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33930; 58190</t>
+          <t>34313; 59117</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26537; 50362</t>
+          <t>26184; 51704</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29101; 55884</t>
+          <t>29094; 54830</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43866; 65836</t>
+          <t>42651; 64949</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71509; 107297</t>
+          <t>72533; 107998</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67900; 106098</t>
+          <t>68186; 105381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67803; 102699</t>
+          <t>67385; 104324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74621; 105998</t>
+          <t>75802; 106439</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12352; 31915</t>
+          <t>11475; 30377</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37491; 65985</t>
+          <t>38482; 68790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26566; 51112</t>
+          <t>26500; 51243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39193; 67681</t>
+          <t>41362; 67893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13477; 32326</t>
+          <t>13769; 32617</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25755; 50159</t>
+          <t>25132; 49666</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27830; 53631</t>
+          <t>26792; 52320</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44506; 65646</t>
+          <t>44802; 67133</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30506; 55427</t>
+          <t>30585; 55647</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69959; 107228</t>
+          <t>69339; 108372</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59986; 94836</t>
+          <t>59327; 94273</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91596; 125901</t>
+          <t>91633; 126175</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48953; 78708</t>
+          <t>49106; 78231</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86881; 127780</t>
+          <t>87409; 126919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63014; 92877</t>
+          <t>60311; 92270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109616; 546217</t>
+          <t>105432; 529329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30067; 52534</t>
+          <t>30334; 51952</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50909; 80508</t>
+          <t>51867; 81279</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29198; 52539</t>
+          <t>28482; 53572</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37657; 55481</t>
+          <t>37475; 55430</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84902; 122261</t>
+          <t>86169; 124666</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146710; 197014</t>
+          <t>148558; 197688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98187; 137752</t>
+          <t>96894; 137899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>158376; 637510</t>
+          <t>159203; 617083</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157150; 204827</t>
+          <t>159144; 206975</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>171964; 226295</t>
+          <t>172053; 225219</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>158190; 206929</t>
+          <t>157564; 209827</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168013; 217312</t>
+          <t>166037; 215008</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>113227; 153590</t>
+          <t>113013; 155752</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102473; 144756</t>
+          <t>101075; 141726</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>117425; 160340</t>
+          <t>116303; 160896</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59700; 162592</t>
+          <t>69624; 162456</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>282532; 345920</t>
+          <t>282208; 344557</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>284335; 352724</t>
+          <t>286397; 352642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>287049; 349946</t>
+          <t>284582; 352323</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>228890; 364900</t>
+          <t>214498; 361132</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37955; 63801</t>
+          <t>37575; 62729</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71568; 105567</t>
+          <t>73217; 107630</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106580; 145990</t>
+          <t>107137; 145818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82691; 118056</t>
+          <t>83258; 119055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95115; 132385</t>
+          <t>94798; 132065</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>227747; 282873</t>
+          <t>230379; 283440</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>189398; 237818</t>
+          <t>185933; 239466</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>153119; 253070</t>
+          <t>164033; 257295</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>140211; 187150</t>
+          <t>140768; 186296</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>311336; 375126</t>
+          <t>314057; 377641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>305689; 369892</t>
+          <t>308201; 373457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>263127; 357164</t>
+          <t>259570; 355775</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3677; 14553</t>
+          <t>3628; 14559</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4858; 18231</t>
+          <t>4913; 18700</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2137; 12856</t>
+          <t>2206; 13713</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1542; 8206</t>
+          <t>1575; 9133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>339504; 405985</t>
+          <t>337566; 403532</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>350360; 415085</t>
+          <t>348778; 413566</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>295311; 361434</t>
+          <t>293841; 361574</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>219264; 261952</t>
+          <t>220521; 263207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>340645; 408841</t>
+          <t>346285; 411571</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>359499; 427712</t>
+          <t>357194; 426567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>300104; 368206</t>
+          <t>301208; 365548</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>219841; 268472</t>
+          <t>220690; 270773</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>333481; 403832</t>
+          <t>330571; 403168</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>452755; 544446</t>
+          <t>458193; 547907</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>429766; 511778</t>
+          <t>429018; 509757</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>480822; 1305741</t>
+          <t>478881; 1212819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>678265; 774330</t>
+          <t>674682; 772142</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>844071; 951682</t>
+          <t>846140; 953387</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>747044; 849928</t>
+          <t>747304; 850605</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>600467; 807702</t>
+          <t>601607; 806960</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1030518; 1147711</t>
+          <t>1035687; 1153199</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1325911; 1470793</t>
+          <t>1336582; 1471608</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1199945; 1334460</t>
+          <t>1200511; 1329948</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1211002; 2321550</t>
+          <t>1213640; 2138993</t>
         </is>
       </c>
     </row>
